--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484086_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484086_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6539</v>
+        <v>4.0479</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1992</v>
+        <v>2.6494</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4546</v>
+        <v>1.3985</v>
       </c>
       <c r="G2" t="n">
         <v>1.6734</v>
@@ -610,13 +610,13 @@
         <v>0.7935</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2266</v>
+        <v>0.6207</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7483</v>
+        <v>0.1985</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4783</v>
+        <v>0.4222</v>
       </c>
       <c r="V2" t="n">
         <v>1.9522</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MALO MONTORIO</t>
+          <t>X. ROSÀS MARCO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4882</v>
+        <v>2.4368</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3205</v>
+        <v>2.9773</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.8323</v>
+        <v>-0.5405</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5429</v>
+        <v>-0.1837</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9797</v>
+        <v>2.9684</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4368</v>
+        <v>-3.1521</v>
       </c>
       <c r="J3" t="n">
-        <v>6.9135</v>
+        <v>2.3214</v>
       </c>
       <c r="K3" t="n">
-        <v>6.2257</v>
+        <v>3.4784</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6879</v>
+        <v>-1.157</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.3706</v>
+        <v>-2.505</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.246</v>
+        <v>-0.51</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.1246</v>
+        <v>-1.9951</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1984</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6098</v>
+        <v>0.8559</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9184</v>
+        <v>0.2268</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6914</v>
+        <v>0.6291</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.4661</v>
+        <v>2.3597</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4724</v>
+        <v>2.4129</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.9386</v>
+        <v>-0.0532</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. ROSÀS MARCO</t>
+          <t>J. MALO MONTORIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1908</v>
+        <v>2.1424</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5068</v>
+        <v>6.9747</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.316</v>
+        <v>-4.8323</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1837</v>
+        <v>3.5429</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9684</v>
+        <v>4.9797</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.1521</v>
+        <v>-1.4368</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3214</v>
+        <v>6.9135</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4784</v>
+        <v>6.2257</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.157</v>
+        <v>0.6879</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.505</v>
+        <v>-3.3706</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.51</v>
+        <v>-1.246</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.9951</v>
+        <v>-2.1246</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5952</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6099</v>
+        <v>1.264</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2436</v>
+        <v>0.5726</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8535</v>
+        <v>0.6914</v>
       </c>
       <c r="V4" t="n">
-        <v>2.3597</v>
+        <v>-2.4661</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4129</v>
+        <v>1.4724</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.0532</v>
+        <v>-3.9386</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PARDINA CERESUELA</t>
+          <t>J. MIRANDA VARGAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1231</v>
+        <v>2.0646</v>
       </c>
       <c r="E5" t="n">
-        <v>3.262</v>
+        <v>4.1623</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.139</v>
+        <v>-2.0977</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1732</v>
+        <v>-1.3404</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0306</v>
+        <v>-0.4036</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1426</v>
+        <v>-0.9367</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1367</v>
+        <v>3.7153</v>
       </c>
       <c r="K5" t="n">
-        <v>1.094</v>
+        <v>1.18</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0427</v>
+        <v>2.5353</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3099</v>
+        <v>-5.0556</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1246</v>
+        <v>-1.5836</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1853</v>
+        <v>-3.472</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.7935</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9919</v>
+        <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>3.0303</v>
+        <v>0.7836</v>
       </c>
       <c r="T5" t="n">
-        <v>2.8512</v>
+        <v>0.2325</v>
       </c>
       <c r="U5" t="n">
-        <v>0.179</v>
+        <v>0.5511</v>
       </c>
       <c r="V5" t="n">
-        <v>0.266</v>
+        <v>1.8278</v>
       </c>
       <c r="W5" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.6213</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MIRANDA VARGAS</t>
+          <t>R. GER SIERRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4742</v>
+        <v>1.2267</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4878</v>
+        <v>2.002</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0136</v>
+        <v>-0.7753</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3404</v>
+        <v>1.1066</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4036</v>
+        <v>1.9449</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9367</v>
+        <v>-0.8383</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7153</v>
+        <v>2.5461</v>
       </c>
       <c r="K6" t="n">
-        <v>1.18</v>
+        <v>2.0565</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5353</v>
+        <v>0.4896</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.0556</v>
+        <v>-1.4395</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5836</v>
+        <v>-0.1116</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.472</v>
+        <v>-1.3279</v>
       </c>
       <c r="P6" t="n">
         <v>0.7935</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7855</v>
+        <v>0.7935</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1933</v>
+        <v>-0.017</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.442</v>
+        <v>-0.5441</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6353</v>
+        <v>0.5271</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8278</v>
+        <v>-0.6564</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6213</v>
+        <v>-0.6564</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. GER SIERRA</t>
+          <t>J. PARDINA CERESUELA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9104</v>
+        <v>0.5467</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7979</v>
+        <v>1.6295</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-1.0828</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1066</v>
+        <v>-1.1732</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9449</v>
+        <v>-0.0306</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8383</v>
+        <v>-1.1426</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5461</v>
+        <v>1.1367</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0565</v>
+        <v>1.094</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4896</v>
+        <v>0.0427</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4395</v>
+        <v>-2.3099</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1116</v>
+        <v>-1.1246</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3279</v>
+        <v>-1.1853</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7935</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3333</v>
+        <v>1.4539</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7481</v>
+        <v>1.2187</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4148</v>
+        <v>0.2352</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6564</v>
+        <v>0.266</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6564</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5736</v>
+        <v>0.1111</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4698</v>
+        <v>1.0422</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0433</v>
+        <v>-0.9311</v>
       </c>
       <c r="G8" t="n">
         <v>-4.6818</v>
@@ -1078,13 +1078,13 @@
         <v>1.5871</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3355</v>
+        <v>1.0203</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1189</v>
+        <v>0.4535</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4545</v>
+        <v>0.5667</v>
       </c>
       <c r="V8" t="n">
         <v>4.1694</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.2608</v>
+        <v>-4.2584</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.8734</v>
+        <v>-4.9551</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6126</v>
+        <v>0.6967</v>
       </c>
       <c r="G9" t="n">
         <v>-3.9845</v>
@@ -1156,13 +1156,13 @@
         <v>0.7935</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.352</v>
+        <v>0.6504</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9238</v>
+        <v>-0.0056</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5718</v>
+        <v>0.656</v>
       </c>
       <c r="V9" t="n">
         <v>0.266</v>
@@ -1189,19 +1189,19 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>8.0062</v>
+        <v>8.317800000000002</v>
       </c>
       <c r="E10" t="n">
-        <v>16.1706</v>
+        <v>16.4823</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.1646</v>
+        <v>-8.164499999999999</v>
       </c>
       <c r="G10" t="n">
         <v>-5.040699999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>7.1053</v>
+        <v>7.105300000000001</v>
       </c>
       <c r="I10" t="n">
         <v>-12.1459</v>
@@ -1234,13 +1234,13 @@
         <v>9.9192</v>
       </c>
       <c r="S10" t="n">
-        <v>6.320099999999999</v>
+        <v>6.6318</v>
       </c>
       <c r="T10" t="n">
-        <v>2.0415</v>
+        <v>2.3529</v>
       </c>
       <c r="U10" t="n">
-        <v>4.2786</v>
+        <v>4.2788</v>
       </c>
       <c r="V10" t="n">
         <v>7.7186</v>
@@ -1249,7 +1249,7 @@
         <v>10.9816</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.2631</v>
+        <v>-3.263100000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.5687</v>
+        <v>4.3503</v>
       </c>
       <c r="E11" t="n">
-        <v>5.3715</v>
+        <v>5.2694</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8027</v>
+        <v>-0.9192</v>
       </c>
       <c r="G11" t="n">
         <v>6.6138</v>
@@ -1312,13 +1312,13 @@
         <v>1.5871</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8712</v>
+        <v>-1.0897</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.731</v>
+        <v>-0.8331</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1402</v>
+        <v>-0.2566</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7771</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. GASSAMA KARGBO</t>
+          <t>P. MULIO CAMPOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5309</v>
+        <v>1.8165</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6024</v>
+        <v>2.195</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0715</v>
+        <v>-0.3786</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5122</v>
+        <v>-0.0437</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1418</v>
+        <v>-0.514</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6296</v>
+        <v>0.4703</v>
       </c>
       <c r="J12" t="n">
-        <v>2.7615</v>
+        <v>2.1925</v>
       </c>
       <c r="K12" t="n">
-        <v>2.6008</v>
+        <v>1.3466</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1606</v>
+        <v>0.8459</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2493</v>
+        <v>-2.2362</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.459</v>
+        <v>-1.8606</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7902</v>
+        <v>-0.3756</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1984</v>
+        <v>1.9838</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7935</v>
+        <v>1.9838</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2171</v>
+        <v>-0.7269</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5669</v>
+        <v>-0.6007</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3498</v>
+        <v>-0.1262</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="W12" t="n">
-        <v>0.266</v>
+        <v>0.6032</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. MULIO CAMPOS</t>
+          <t>B. GASSAMA KARGBO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8617</v>
+        <v>1.2869</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6849</v>
+        <v>2.1943</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8232</v>
+        <v>-0.9074</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0437</v>
+        <v>1.5122</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.514</v>
+        <v>2.1418</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4703</v>
+        <v>-0.6296</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1925</v>
+        <v>2.7615</v>
       </c>
       <c r="K13" t="n">
-        <v>1.3466</v>
+        <v>2.6008</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8459</v>
+        <v>0.1606</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.2362</v>
+        <v>-1.2493</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8606</v>
+        <v>-0.459</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3756</v>
+        <v>-0.7902</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9838</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9838</v>
+        <v>0.7935</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6817</v>
+        <v>-0.0269</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1109</v>
+        <v>0.1587</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5708</v>
+        <v>-0.1857</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6032</v>
+        <v>0.266</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2695</v>
+        <v>0.2747</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3293</v>
+        <v>1.7374</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5987</v>
+        <v>-1.4627</v>
       </c>
       <c r="G14" t="n">
         <v>0.2708</v>
@@ -1546,13 +1546,13 @@
         <v>1.7855</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6721</v>
+        <v>-1.128</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4849</v>
+        <v>-1.0768</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1872</v>
+        <v>-0.0511</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6536</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3845</v>
+        <v>-0.1703</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7954</v>
+        <v>-0.6934</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4109</v>
+        <v>0.5231</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5444</v>
@@ -1624,13 +1624,13 @@
         <v>0.3968</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2369</v>
+        <v>-0.0227</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1757</v>
+        <v>-0.0737</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0612</v>
+        <v>0.051</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>,. VICENTE SABARIEGO</t>
+          <t>M. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.771</v>
+        <v>-0.9495</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6022999999999999</v>
+        <v>1.3185</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3733</v>
+        <v>-2.268</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9083</v>
+        <v>-0.3534</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9083</v>
+        <v>-1.8044</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1.4509</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9083</v>
+        <v>0.2205</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9083</v>
+        <v>-0.2717</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.4921</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-0.5739</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-1.5327</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.9588</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.9919</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7968</v>
+        <v>-0.4223</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3604</v>
+        <v>-0.323</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4364</v>
+        <v>-0.0993</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.4842</v>
+        <v>-0.1738</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6745</v>
+        <v>2.4129</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.8097</v>
+        <v>-2.5868</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MAÑES CARRETERO</t>
+          <t>A. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8016</v>
+        <v>-1.1039</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5225</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3241</v>
+        <v>-1.1977</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3534</v>
+        <v>-0.0883</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8044</v>
+        <v>0.5945</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4509</v>
+        <v>-0.6827</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2205</v>
+        <v>0.4282</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2717</v>
+        <v>0.9879</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4921</v>
+        <v>-0.5597</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5739</v>
+        <v>-0.5165</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5327</v>
+        <v>-0.3935</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9588</v>
+        <v>-0.123</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.1984</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9919</v>
+        <v>0.1984</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2743</v>
+        <v>-0.948</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1189</v>
+        <v>-0.3344</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1554</v>
+        <v>-0.6136</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1738</v>
+        <v>-0.266</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4129</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.5868</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CRUZ URBANEJA</t>
+          <t>J. ARNAL DIAZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2901</v>
+        <v>-1.2824</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.9923999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2819</v>
+        <v>-0.2899</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0883</v>
+        <v>1.1612</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5945</v>
+        <v>-0.378</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6827</v>
+        <v>1.5391</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4282</v>
+        <v>1.2582</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9879</v>
+        <v>0.0106</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5597</v>
+        <v>1.2476</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5165</v>
+        <v>-0.097</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3935</v>
+        <v>-0.3886</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.123</v>
+        <v>0.2916</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1984</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1984</v>
+        <v>0.7935</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1342</v>
+        <v>-0.4761</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4364</v>
+        <v>-0.5327</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6978</v>
+        <v>0.0566</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.266</v>
+        <v>-0.7771</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.266</v>
+        <v>-1.0431</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ARNAL DIAZ</t>
+          <t>,. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.398</v>
+        <v>-1.7743</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1965</v>
+        <v>-0.214</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2015</v>
+        <v>-1.5603</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1612</v>
+        <v>0.9083</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.378</v>
+        <v>0.9083</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5391</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2582</v>
+        <v>0.9083</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0106</v>
+        <v>0.9083</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2476</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.097</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3886</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2916</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.7935</v>
       </c>
-      <c r="S19" t="n">
-        <v>-0.5918</v>
-      </c>
       <c r="T19" t="n">
-        <v>-0.7368</v>
+        <v>0.5442</v>
       </c>
       <c r="U19" t="n">
-        <v>0.145</v>
+        <v>0.2494</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7771</v>
+        <v>-2.4842</v>
       </c>
       <c r="W19" t="n">
-        <v>0.266</v>
+        <v>-0.6745</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0431</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7385</v>
+        <v>-2.282</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0892</v>
+        <v>0.1149</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6493</v>
+        <v>-2.3968</v>
       </c>
       <c r="G20" t="n">
         <v>-2.8049</v>
@@ -2010,13 +2010,13 @@
         <v>0.9919</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9256</v>
+        <v>-0.469</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6121</v>
+        <v>-0.408</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3135</v>
+        <v>-0.061</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2043,13 +2043,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7385</v>
+        <v>-2.282</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0892</v>
+        <v>0.1149</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6493</v>
+        <v>-2.3968</v>
       </c>
       <c r="G21" t="n">
         <v>-2.8049</v>
@@ -2088,13 +2088,13 @@
         <v>0.9919</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9256</v>
+        <v>-0.469</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6121</v>
+        <v>-0.408</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3135</v>
+        <v>-0.061</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2121,13 +2121,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.3142</v>
+        <v>-7.1943</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.859</v>
+        <v>-2.6549</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.4553</v>
+        <v>-4.5394</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5911</v>
@@ -2166,13 +2166,13 @@
         <v>1.3887</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.946</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7991</v>
+        <v>-0.5951</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1469</v>
+        <v>-0.2311</v>
       </c>
       <c r="V22" t="n">
         <v>-3.19</v>
@@ -2199,16 +2199,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.7446</v>
+        <v>-9.3103</v>
       </c>
       <c r="E23" t="n">
-        <v>8.075399999999998</v>
+        <v>8.483500000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-18.8199</v>
+        <v>-17.7937</v>
       </c>
       <c r="G23" t="n">
-        <v>2.235600000000002</v>
+        <v>2.235600000000001</v>
       </c>
       <c r="H23" t="n">
         <v>-8.9102</v>
@@ -2244,13 +2244,13 @@
         <v>11.903</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.2455</v>
+        <v>-5.811200000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.8906</v>
+        <v>-4.4826</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.3549</v>
+        <v>-1.3286</v>
       </c>
       <c r="V23" t="n">
         <v>-7.7186</v>
